--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -373,7 +373,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -673,7 +673,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|Appointment|AppointmentResponse|Task)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
 </t>
   </si>
   <si>
@@ -752,7 +752,7 @@
     <t>ImagingStudy.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -881,7 +881,7 @@
     <t>ImagingStudy.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -932,7 +932,7 @@
     <t>研究の理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1264,7 +1264,7 @@
     <t>ImagingStudy.series.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1356,7 +1356,7 @@
     <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/series-performer-function|4.0.1</t>
   </si>
   <si>
     <t>ImagingStudy.series.performer.actor</t>
